--- a/StructureDefinition-tk-api-specification-capability.xlsx
+++ b/StructureDefinition-tk-api-specification-capability.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="628">
   <si>
     <t>Property</t>
   </si>
@@ -594,13 +594,16 @@
 </t>
   </si>
   <si>
-    <t>Business version of the capability statement</t>
+    <t>Specifikationens version. url + version är unik i katalogen</t>
   </si>
   <si>
     <t>The identifier that is used to identify this version of the capability statement when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the capability statement author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence.</t>
   </si>
   <si>
     <t>There may be different capability statement instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the capability statement with the format [url]|[version]. The version SHOULD NOT contain a '#' - see [Business Version](http://hl7.org/fhir/R5/resource.html#bv-format).</t>
+  </si>
+  <si>
+    <t>REQ-MDL-4, REQ-MDL-8</t>
   </si>
   <si>
     <t>FiveWs.version</t>
@@ -4077,7 +4080,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>89</v>
@@ -4166,10 +4169,10 @@
         <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>148</v>
+        <v>184</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>78</v>
@@ -4180,10 +4183,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4206,16 +4209,16 @@
         <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4241,11 +4244,11 @@
         <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>78</v>
@@ -4263,7 +4266,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -4292,10 +4295,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4321,16 +4324,16 @@
         <v>180</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4379,7 +4382,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -4388,7 +4391,7 @@
         <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>101</v>
@@ -4408,10 +4411,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4437,13 +4440,13 @@
         <v>180</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4493,7 +4496,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -4522,10 +4525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4551,13 +4554,13 @@
         <v>109</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4586,10 +4589,10 @@
         <v>113</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>78</v>
@@ -4607,7 +4610,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>89</v>
@@ -4625,7 +4628,7 @@
         <v>148</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>78</v>
@@ -4636,10 +4639,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4662,70 +4665,70 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="P21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="R21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF21" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="L21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="P21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="R21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE21" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF21" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4743,7 +4746,7 @@
         <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>78</v>
@@ -4754,14 +4757,14 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4780,16 +4783,16 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4839,7 +4842,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>89</v>
@@ -4857,7 +4860,7 @@
         <v>148</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>78</v>
@@ -4868,10 +4871,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4897,16 +4900,16 @@
         <v>180</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>78</v>
@@ -4955,7 +4958,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -4973,7 +4976,7 @@
         <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>78</v>
@@ -4984,10 +4987,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5010,16 +5013,16 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5069,7 +5072,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -5098,10 +5101,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5124,16 +5127,16 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5183,7 +5186,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5192,7 +5195,7 @@
         <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>101</v>
@@ -5212,10 +5215,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5238,19 +5241,19 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5299,7 +5302,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5328,10 +5331,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5354,16 +5357,16 @@
         <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5389,13 +5392,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5413,7 +5416,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5442,10 +5445,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5468,16 +5471,16 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5527,7 +5530,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5545,25 +5548,25 @@
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5582,19 +5585,19 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
@@ -5643,7 +5646,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5667,15 +5670,15 @@
         <v>78</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5701,16 +5704,16 @@
         <v>180</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5759,7 +5762,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5788,10 +5791,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5817,14 +5820,14 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -5834,7 +5837,7 @@
         <v>78</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>78</v>
@@ -5852,10 +5855,10 @@
         <v>113</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
@@ -5873,7 +5876,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>89</v>
@@ -5882,7 +5885,7 @@
         <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>101</v>
@@ -5902,10 +5905,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5928,16 +5931,16 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5987,7 +5990,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6016,10 +6019,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6042,16 +6045,16 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6101,7 +6104,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6130,10 +6133,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6156,13 +6159,13 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6213,7 +6216,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6222,7 +6225,7 @@
         <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>101</v>
@@ -6242,10 +6245,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6271,10 +6274,10 @@
         <v>180</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6325,7 +6328,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6334,7 +6337,7 @@
         <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
@@ -6354,10 +6357,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6383,10 +6386,10 @@
         <v>136</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>163</v>
@@ -6439,7 +6442,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6468,14 +6471,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6497,10 +6500,10 @@
         <v>136</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>163</v>
@@ -6555,7 +6558,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -6584,10 +6587,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6613,10 +6616,10 @@
         <v>180</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6667,7 +6670,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>89</v>
@@ -6696,10 +6699,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6725,13 +6728,13 @@
         <v>180</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6781,7 +6784,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6810,10 +6813,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6836,13 +6839,13 @@
         <v>90</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6893,7 +6896,7 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6922,10 +6925,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6948,13 +6951,13 @@
         <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7005,7 +7008,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7014,7 +7017,7 @@
         <v>89</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>101</v>
@@ -7034,10 +7037,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7063,10 +7066,10 @@
         <v>180</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7117,7 +7120,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7126,7 +7129,7 @@
         <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>78</v>
@@ -7146,10 +7149,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7175,10 +7178,10 @@
         <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>163</v>
@@ -7231,7 +7234,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7260,14 +7263,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7289,10 +7292,10 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>163</v>
@@ -7347,7 +7350,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7376,10 +7379,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7402,13 +7405,13 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7459,7 +7462,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>89</v>
@@ -7488,10 +7491,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7514,13 +7517,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7571,7 +7574,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7600,10 +7603,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7626,13 +7629,13 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7683,7 +7686,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7712,10 +7715,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7741,13 +7744,13 @@
         <v>109</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7776,10 +7779,10 @@
         <v>113</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7797,7 +7800,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>89</v>
@@ -7826,10 +7829,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7855,13 +7858,13 @@
         <v>109</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7890,10 +7893,10 @@
         <v>113</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -7911,7 +7914,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>89</v>
@@ -7940,10 +7943,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7969,13 +7972,13 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8004,10 +8007,10 @@
         <v>113</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>78</v>
@@ -8025,7 +8028,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8054,10 +8057,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8083,13 +8086,13 @@
         <v>109</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8139,7 +8142,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8168,10 +8171,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8194,16 +8197,16 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8253,7 +8256,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8282,10 +8285,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8308,16 +8311,16 @@
         <v>90</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8367,7 +8370,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8376,10 +8379,10 @@
         <v>80</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8396,10 +8399,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8425,10 +8428,10 @@
         <v>180</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8479,7 +8482,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8488,7 +8491,7 @@
         <v>89</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>78</v>
@@ -8508,10 +8511,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8537,10 +8540,10 @@
         <v>136</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>163</v>
@@ -8593,7 +8596,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8622,14 +8625,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8651,10 +8654,10 @@
         <v>136</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>163</v>
@@ -8709,7 +8712,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8738,10 +8741,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8767,10 +8770,10 @@
         <v>109</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8782,7 +8785,7 @@
         <v>78</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>78</v>
@@ -8800,10 +8803,10 @@
         <v>113</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>78</v>
@@ -8821,7 +8824,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>89</v>
@@ -8830,7 +8833,7 @@
         <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>101</v>
@@ -8850,10 +8853,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8876,13 +8879,13 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8933,7 +8936,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -8962,10 +8965,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8988,13 +8991,13 @@
         <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9045,7 +9048,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9074,10 +9077,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9103,10 +9106,10 @@
         <v>180</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9157,7 +9160,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9166,7 +9169,7 @@
         <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>78</v>
@@ -9186,10 +9189,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9215,10 +9218,10 @@
         <v>136</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>163</v>
@@ -9271,7 +9274,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9300,14 +9303,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9329,10 +9332,10 @@
         <v>136</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>163</v>
@@ -9387,7 +9390,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -9416,10 +9419,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9442,16 +9445,16 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9501,7 +9504,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9530,10 +9533,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9556,13 +9559,13 @@
         <v>90</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9589,13 +9592,13 @@
         <v>78</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9613,7 +9616,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9642,10 +9645,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9668,13 +9671,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9725,7 +9728,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -9754,10 +9757,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9780,16 +9783,16 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9839,7 +9842,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9848,10 +9851,10 @@
         <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -9868,10 +9871,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9897,10 +9900,10 @@
         <v>180</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9951,7 +9954,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -9960,7 +9963,7 @@
         <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>78</v>
@@ -9980,10 +9983,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10009,10 +10012,10 @@
         <v>136</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>163</v>
@@ -10065,7 +10068,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10094,14 +10097,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10123,10 +10126,10 @@
         <v>136</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>163</v>
@@ -10181,7 +10184,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10210,10 +10213,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10239,10 +10242,10 @@
         <v>109</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10272,10 +10275,10 @@
         <v>113</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10293,7 +10296,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>89</v>
@@ -10302,7 +10305,7 @@
         <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>101</v>
@@ -10322,10 +10325,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10348,16 +10351,16 @@
         <v>90</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10407,7 +10410,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10436,10 +10439,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10462,16 +10465,16 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10521,7 +10524,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10550,10 +10553,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10576,13 +10579,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10633,7 +10636,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10662,10 +10665,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10688,16 +10691,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10747,7 +10750,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
@@ -10776,10 +10779,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10805,10 +10808,10 @@
         <v>180</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10859,7 +10862,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -10868,7 +10871,7 @@
         <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>78</v>
@@ -10888,10 +10891,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10917,10 +10920,10 @@
         <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>163</v>
@@ -10973,7 +10976,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11002,14 +11005,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11031,10 +11034,10 @@
         <v>136</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>163</v>
@@ -11089,7 +11092,7 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11118,10 +11121,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11147,10 +11150,10 @@
         <v>109</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11180,10 +11183,10 @@
         <v>113</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>78</v>
@@ -11201,7 +11204,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>89</v>
@@ -11230,10 +11233,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11256,17 +11259,17 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
@@ -11315,7 +11318,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11344,10 +11347,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11373,13 +11376,13 @@
         <v>109</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11408,10 +11411,10 @@
         <v>113</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11429,7 +11432,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11458,10 +11461,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11484,16 +11487,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11543,7 +11546,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11572,10 +11575,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11598,16 +11601,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11657,7 +11660,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11686,10 +11689,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11712,16 +11715,16 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -11771,7 +11774,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -11800,10 +11803,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11829,13 +11832,13 @@
         <v>109</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11864,10 +11867,10 @@
         <v>113</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>78</v>
@@ -11885,7 +11888,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -11914,10 +11917,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11940,16 +11943,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11999,7 +12002,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12028,10 +12031,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12054,16 +12057,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12113,7 +12116,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12142,10 +12145,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12171,13 +12174,13 @@
         <v>109</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12206,10 +12209,10 @@
         <v>113</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>78</v>
@@ -12227,7 +12230,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12256,10 +12259,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12285,10 +12288,10 @@
         <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12318,10 +12321,10 @@
         <v>113</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>78</v>
@@ -12339,7 +12342,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12368,10 +12371,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12397,13 +12400,13 @@
         <v>180</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12453,7 +12456,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12482,10 +12485,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12511,13 +12514,13 @@
         <v>180</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12567,7 +12570,7 @@
         <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>79</v>
@@ -12596,10 +12599,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12622,16 +12625,16 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12681,7 +12684,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -12690,7 +12693,7 @@
         <v>80</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>101</v>
@@ -12710,10 +12713,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12739,10 +12742,10 @@
         <v>180</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12793,7 +12796,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -12802,7 +12805,7 @@
         <v>89</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>78</v>
@@ -12822,10 +12825,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12851,10 +12854,10 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>163</v>
@@ -12907,7 +12910,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -12936,14 +12939,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12965,10 +12968,10 @@
         <v>136</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>163</v>
@@ -13023,7 +13026,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13052,10 +13055,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13081,13 +13084,13 @@
         <v>180</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13137,7 +13140,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>89</v>
@@ -13146,7 +13149,7 @@
         <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AJ95" t="s" s="2">
         <v>101</v>
@@ -13166,10 +13169,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13192,16 +13195,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13251,7 +13254,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13280,10 +13283,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13309,13 +13312,13 @@
         <v>109</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13344,10 +13347,10 @@
         <v>113</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>78</v>
@@ -13365,7 +13368,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>89</v>
@@ -13394,10 +13397,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13420,13 +13423,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13477,7 +13480,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13506,10 +13509,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13532,16 +13535,16 @@
         <v>90</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13591,7 +13594,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
@@ -13620,10 +13623,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13649,10 +13652,10 @@
         <v>180</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13703,7 +13706,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -13712,7 +13715,7 @@
         <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>78</v>
@@ -13732,10 +13735,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13761,10 +13764,10 @@
         <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>163</v>
@@ -13817,7 +13820,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -13846,14 +13849,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -13875,10 +13878,10 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>163</v>
@@ -13933,7 +13936,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -13962,10 +13965,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13991,13 +13994,13 @@
         <v>180</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14047,7 +14050,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>89</v>
@@ -14076,10 +14079,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14102,16 +14105,16 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14161,7 +14164,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>89</v>
@@ -14190,10 +14193,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14216,13 +14219,13 @@
         <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -14273,7 +14276,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14302,10 +14305,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14328,13 +14331,13 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14385,7 +14388,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14414,10 +14417,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14443,10 +14446,10 @@
         <v>180</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14497,7 +14500,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14506,7 +14509,7 @@
         <v>89</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>78</v>
@@ -14526,10 +14529,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14555,10 +14558,10 @@
         <v>136</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N108" t="s" s="2">
         <v>163</v>
@@ -14611,7 +14614,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -14640,14 +14643,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14669,10 +14672,10 @@
         <v>136</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N109" t="s" s="2">
         <v>163</v>
@@ -14727,7 +14730,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -14756,10 +14759,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14785,10 +14788,10 @@
         <v>109</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14818,10 +14821,10 @@
         <v>113</v>
       </c>
       <c r="Y110" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="Z110" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>78</v>
@@ -14839,7 +14842,7 @@
         <v>78</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>89</v>
@@ -14868,10 +14871,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14894,13 +14897,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14951,7 +14954,7 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
@@ -14980,10 +14983,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15009,13 +15012,13 @@
         <v>81</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15065,7 +15068,7 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
@@ -15094,10 +15097,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15123,13 +15126,13 @@
         <v>81</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15179,7 +15182,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15208,10 +15211,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15234,16 +15237,16 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -15293,7 +15296,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
@@ -15322,10 +15325,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15348,16 +15351,16 @@
         <v>90</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -15407,7 +15410,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -15416,7 +15419,7 @@
         <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -15436,10 +15439,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15465,10 +15468,10 @@
         <v>180</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15519,7 +15522,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15528,7 +15531,7 @@
         <v>89</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>78</v>
@@ -15548,10 +15551,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15577,10 +15580,10 @@
         <v>136</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>163</v>
@@ -15633,7 +15636,7 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
@@ -15662,14 +15665,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15691,10 +15694,10 @@
         <v>136</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>163</v>
@@ -15749,7 +15752,7 @@
         <v>78</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>79</v>
@@ -15778,14 +15781,14 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
@@ -15804,13 +15807,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -15861,7 +15864,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -15870,7 +15873,7 @@
         <v>80</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>101</v>
@@ -15890,10 +15893,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15919,10 +15922,10 @@
         <v>180</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -15973,7 +15976,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -15982,7 +15985,7 @@
         <v>89</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>78</v>
@@ -16002,10 +16005,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16031,10 +16034,10 @@
         <v>136</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N121" t="s" s="2">
         <v>163</v>
@@ -16087,7 +16090,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -16116,14 +16119,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -16145,10 +16148,10 @@
         <v>136</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>163</v>
@@ -16203,7 +16206,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -16232,10 +16235,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16258,13 +16261,13 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -16291,13 +16294,13 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16315,7 +16318,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>89</v>
@@ -16344,10 +16347,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16370,13 +16373,13 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -16427,7 +16430,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>89</v>
@@ -16456,10 +16459,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16482,16 +16485,16 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -16541,7 +16544,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -16570,10 +16573,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16596,13 +16599,13 @@
         <v>78</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16653,7 +16656,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -16682,10 +16685,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16708,16 +16711,16 @@
         <v>90</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -16767,7 +16770,7 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
@@ -16796,10 +16799,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -16825,10 +16828,10 @@
         <v>180</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -16879,7 +16882,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -16888,7 +16891,7 @@
         <v>89</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>78</v>
@@ -16908,10 +16911,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -16937,10 +16940,10 @@
         <v>136</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N129" t="s" s="2">
         <v>163</v>
@@ -16993,7 +16996,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17022,14 +17025,14 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -17051,10 +17054,10 @@
         <v>136</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N130" t="s" s="2">
         <v>163</v>
@@ -17109,7 +17112,7 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
@@ -17138,10 +17141,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17167,10 +17170,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17200,10 +17203,10 @@
         <v>113</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>78</v>
@@ -17221,7 +17224,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>89</v>
@@ -17250,10 +17253,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17276,13 +17279,13 @@
         <v>90</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -17333,7 +17336,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>89</v>
@@ -17362,10 +17365,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17388,13 +17391,13 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -17445,7 +17448,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17454,7 +17457,7 @@
         <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>101</v>
@@ -17474,10 +17477,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17503,10 +17506,10 @@
         <v>180</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -17557,7 +17560,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -17566,7 +17569,7 @@
         <v>89</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>78</v>
@@ -17586,10 +17589,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17615,10 +17618,10 @@
         <v>136</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N135" t="s" s="2">
         <v>163</v>
@@ -17671,7 +17674,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -17700,14 +17703,14 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
@@ -17729,10 +17732,10 @@
         <v>136</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>163</v>
@@ -17787,7 +17790,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -17816,10 +17819,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17845,10 +17848,10 @@
         <v>109</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -17878,10 +17881,10 @@
         <v>113</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -17899,7 +17902,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>89</v>
@@ -17908,7 +17911,7 @@
         <v>89</v>
       </c>
       <c r="AI137" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AJ137" t="s" s="2">
         <v>101</v>
@@ -17928,10 +17931,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -17954,13 +17957,13 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -18011,7 +18014,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -18040,10 +18043,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18066,16 +18069,16 @@
         <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18125,7 +18128,7 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>89</v>
@@ -18134,7 +18137,7 @@
         <v>89</v>
       </c>
       <c r="AI139" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AJ139" t="s" s="2">
         <v>101</v>
